--- a/docs/xlsx/jobs-2026-08-20.xlsx
+++ b/docs/xlsx/jobs-2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="617">
   <si>
     <t>Title</t>
   </si>
@@ -61,21 +61,27 @@
     <t>https://www.conservationjobboard.com/job-listing-administrative-coordinator-seattle-washington/1121012071</t>
   </si>
   <si>
+    <t>Adult Salmonid Trapping and Evaluation Biologist - Fish &amp; Wildlife Biologist 3 - Permanent - 2026-06957</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Dayton, WA</t>
+  </si>
+  <si>
+    <t>$5,642 - $7,592 per month</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adult-salmonid-trapping-and-evaluation-biologist---fish--wildlife-biologist-3---permanent---2026-06957-dayton-washington/5307490012</t>
+  </si>
+  <si>
     <t>Adult Trapping and Evaluation Biologist - Fish &amp; Wildlife Biologist 3 - Permanent - 2026-06957</t>
   </si>
   <si>
-    <t>Washington Department of Fish and Wildlife</t>
-  </si>
-  <si>
-    <t>Dayton, WA</t>
-  </si>
-  <si>
-    <t>$5,642 - $7,592 per month</t>
-  </si>
-  <si>
-    <t>fisheries</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-adult-trapping-and-evaluation-biologist---fish--wildlife-biologist-3---permanent---2026-06957-dayton-washington/5307490012</t>
   </si>
   <si>
@@ -538,6 +544,27 @@
     <t>https://www.conservationjobboard.com/job-listing-watershed-restoration-program-manager-patagonia-arizona/2757376238</t>
   </si>
   <si>
+    <t>Accounts Payable Specialist (3+ Years AP Exp REQUIRED)</t>
+  </si>
+  <si>
+    <t>International Cinematographers Guild, Local 600, IATSE</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 31.51 - 34.61/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77cb3bd35ace484b8ead96c8c56380d8-accounts-payable-specialist-3-years-ap-exp-required-international-cinematographers-guild-local-600-iatse-los-angeles</t>
+  </si>
+  <si>
     <t>Admin and Operations Coordinator</t>
   </si>
   <si>
@@ -547,9 +574,6 @@
     <t>Saint Paul, Minnesota</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 45000.00 - 48000.00/year</t>
   </si>
   <si>
@@ -559,6 +583,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/caf47afb8ecf466f84638620c2311bed-admin-and-operations-coordinator-brownbody-saint-paul</t>
   </si>
   <si>
+    <t>Administrative and Program Coordinator</t>
+  </si>
+  <si>
+    <t>Resident Association of Greater Englewood</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc80d398ea7441d5b0061c618ec21e8e-administrative-and-program-coordinator-resident-association-of-greater-englewood-chicago</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -595,6 +637,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/30978d5c728844c899f12d1335be8ab7-admissions-manager-mattapan-residential-boston-public-health-commission-boston</t>
   </si>
   <si>
+    <t>Advisory Programs Contractor</t>
+  </si>
+  <si>
+    <t>The Lenfest Institute for Journalism</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 3500.00 - 3500.00/month</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/deef75ba6b1645d094e5542ba7904f05-advisory-programs-contractor-the-lenfest-institute-for-journalism-philadelphia</t>
+  </si>
+  <si>
     <t>Appellate Advocacy Fellow</t>
   </si>
   <si>
@@ -613,15 +676,270 @@
     <t>https://www.idealist.org/en/nonprofit-job/66526055e21846c7b5b8112b85c53a34-appellate-advocacy-fellow-legal-aid-dc-washington</t>
   </si>
   <si>
+    <t>ASE (Adolescent Sexuality Education) Health &amp; Wellness Peer Educator</t>
+  </si>
+  <si>
+    <t>BAGLY Inc.</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fe37acc6dea45299b73ad2cda684f62-ase-adolescent-sexuality-education-health-wellness-peer-educator-bagly-inc-boston</t>
+  </si>
+  <si>
+    <t>Asistente Administrativo/a Remoto/a – Clínica Virtual</t>
+  </si>
+  <si>
+    <t>Clínica Virtual - Especializada en salud mental</t>
+  </si>
+  <si>
+    <t>USD 0.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Lgbtq, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/4a1de6453ea54c92ba8475581d579bcc-asistente-administrativoa-remotoa-clinica-virtual-clinica-virtual-especializada-en-salud-mental-buenos-aires</t>
+  </si>
+  <si>
+    <t>Assistant Director, Budgets and Grants - JFNA</t>
+  </si>
+  <si>
+    <t>Jewish Federations of North America</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cfe3564b1c54c1284a94c3eba2991f2-assistant-director-budgets-and-grants-jfna-jewish-federations-of-north-america-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Manager of Development and Marketing</t>
+  </si>
+  <si>
+    <t>Pitney Meadows Community Farm</t>
+  </si>
+  <si>
+    <t>Saratoga Springs, New York</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c2257421d5c49d4bc15c7c83d76decf-assistant-manager-of-development-and-marketing-pitney-meadows-community-farm-saratoga-springs</t>
+  </si>
+  <si>
+    <t>Assistant Theater Manager, LCT3 / Claire Tow Theater</t>
+  </si>
+  <si>
+    <t>Lincoln Center Theater - New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d8cd2001be4402e8287d4e4385516db-assistant-theater-manager-lct3-claire-tow-theater-lincoln-center-theater-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Associate Director, Advancement &amp; Engagement Palm Beach</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78958991d890480e814a0aa66720e927-associate-director-advancement-engagement-palm-beach-ajc-palm-beach</t>
+  </si>
+  <si>
+    <t>Associate Director, Bay Area Local Advocacy</t>
+  </si>
+  <si>
+    <t>California Charter Schools Association</t>
+  </si>
+  <si>
+    <t>Remote (Oakland, California)</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 75720.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77163635f66f451789728a4ab5913a1c-associate-director-bay-area-local-advocacy-california-charter-schools-association-oakland</t>
+  </si>
+  <si>
+    <t>Associate Director, Education Programing</t>
+  </si>
+  <si>
+    <t>RiseBoro Community Partnership</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2be264123bd4a0d9320f0788d09f6eb-associate-director-education-programing-riseboro-community-partnership-kings-county</t>
+  </si>
+  <si>
+    <t>Associate Registrar</t>
+  </si>
+  <si>
+    <t>The Isamu Noguchi Foundation and Garden Museum</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/001bc85e9e6543c094186664338dd077-associate-registrar-the-isamu-noguchi-foundation-and-garden-museum-queens-county</t>
+  </si>
+  <si>
+    <t>Associate, Program Delivery &amp; Operations</t>
+  </si>
+  <si>
+    <t>THE ERIC AND WENDY SCHMIDT FUND FOR STRATEGIC INNOVATION</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cd146b2a58945469af4ee3c1749c9d4-associate-program-delivery-operations-the-eric-and-wendy-schmidt-fund-for-strategic-innovation-new-york</t>
+  </si>
+  <si>
+    <t>Become a Campus Organizer in Springfield, MO!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Springfield, Missouri</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8fbb5e77c4e94c40b08beb03d808e9e1-become-a-campus-organizer-in-springfield-mo-the-outreach-team-springfield</t>
+  </si>
+  <si>
+    <t>Business Development Manager</t>
+  </si>
+  <si>
+    <t>CIF- The Community Impact Fund</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Financial Literacy Personal Finance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11d6257327384f9e9971dc44fc9a3f52-business-development-manager-cif-the-community-impact-fund-greenwood-village</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Holt International</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon</t>
+  </si>
+  <si>
+    <t>USD 250000.00 - 300000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/aa6c5f5ad18f48888e981ec57fed7392-chief-executive-officer-holt-international-eugene</t>
+  </si>
+  <si>
+    <t>Child Care Policy Research Analyst (Research Analyst 3)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Early Learning and Care</t>
+  </si>
+  <si>
+    <t>Salem, Oregon</t>
+  </si>
+  <si>
+    <t>USD 5193.00 - 7968.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/74159533fc134b15ad7b6d282da082e7-child-care-policy-research-analyst-research-analyst-3-oregon-department-of-early-learning-and-care-salem</t>
+  </si>
+  <si>
+    <t>Contracts and Legal Operations Manager</t>
+  </si>
+  <si>
+    <t>Everytown For Gun Safety</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e402d250c6741d3bbcbcc7e9c963a90-contracts-and-legal-operations-manager-everytown-for-gun-safety-new-york</t>
+  </si>
+  <si>
+    <t>Controller (Contract Position)</t>
+  </si>
+  <si>
+    <t>Bethany Baptist Church</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 80.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb8b6284e8bc4ff9861f2cc2ece20ac3-controller-contract-position-bethany-baptist-church-newark</t>
+  </si>
+  <si>
     <t>Coordinator, Chicago DRO</t>
   </si>
   <si>
-    <t>AJC</t>
-  </si>
-  <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 50000.00 - 55000.00/year</t>
   </si>
   <si>
@@ -631,6 +949,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/515892379fc54ab78509fa6b721507f2-coordinator-chicago-dro-ajc-chicago</t>
   </si>
   <si>
+    <t>Corporate Partnerships Manager</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72c65be6e15041b0b00dbaaaf7e75b73-corporate-partnerships-manager-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Counsel</t>
   </si>
   <si>
@@ -646,6 +979,39 @@
     <t>https://www.idealist.org/en/job/2681420451694fa3a191232e3d3689f7-counsel-american-psychological-association-washington</t>
   </si>
   <si>
+    <t>Creative Aging Program Manager</t>
+  </si>
+  <si>
+    <t>Goddard House in Brookline Assisted Living</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>Philanthropy, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/461c629a9d644507a1c4464f3f50346a-creative-aging-program-manager-goddard-house-in-brookline-assisted-living-brookline</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 32.42 - 37.47/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c3117cead254edc83b65a629a53b061-data-analyst-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
     <t>Database Manager</t>
   </si>
   <si>
@@ -658,6 +1024,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/df23fe9ecd8e43f39135bf4a85b14a48-database-manager-the-aloha-foundation-fairlee</t>
   </si>
   <si>
+    <t>Department Administrator</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fe87b65ed954ef9b475270119021d6d-department-administrator-civilization-research-institute-asheville</t>
+  </si>
+  <si>
+    <t>Development &amp; Marketing Manager (Full-Time)</t>
+  </si>
+  <si>
+    <t>Vocal Youth Miami</t>
+  </si>
+  <si>
+    <t>Palmetto Bay, Florida</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f5e84bc451c427cae60dff322c2b5dc-development-marketing-manager-full-time-vocal-youth-miami-palmetto-bay</t>
+  </si>
+  <si>
     <t>Development Associate</t>
   </si>
   <si>
@@ -691,15 +1087,234 @@
     <t>https://www.idealist.org/en/nonprofit-job/8ceefb8d52684e5fb6c1d7aa01d5cf5a-development-coordinator-health-care-for-all-boston</t>
   </si>
   <si>
+    <t>Development Director OR Deputy Chief of Staff</t>
+  </si>
+  <si>
+    <t>Policing Project</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c524f2ef0944482a89bc7ffddfe9877-development-director-or-deputy-chief-of-staff-policing-project-new-york</t>
+  </si>
+  <si>
+    <t>Director of Advancement Operations and Annual Giving</t>
+  </si>
+  <si>
+    <t>Hill Museum &amp; Manuscript Library</t>
+  </si>
+  <si>
+    <t>Remote (Minnesota)</t>
+  </si>
+  <si>
+    <t>Education, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b98c60d99ce44a5a1e745b718b49b38-director-of-advancement-operations-and-annual-giving-hill-museum-manuscript-library-st-cloud</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Fort Greene Park Conservancy</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c27161279ec494a959efd95a0a096ce-director-of-development-fort-greene-park-conservancy-kings-county</t>
+  </si>
+  <si>
+    <t>Director of Editorial Events</t>
+  </si>
+  <si>
+    <t>CalMatters</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3253257dfd3648b0b32bad1096b800fc-director-of-editorial-events-calmatters-sacramento</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Sakhi for South Asian Survivors</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43bb4738c8534f6591164f277451928b-director-of-programs-sakhi-for-south-asian-survivors-new-york</t>
+  </si>
+  <si>
+    <t>Evening Program Assistant</t>
+  </si>
+  <si>
+    <t>Math for America (MfA) NYC</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/503aed10ed44459299ed8555a1eb80d6-evening-program-assistant-math-for-america-mfa-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Event Producer</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1dc008491bd74737b8b6cc257c5f459f-event-producer-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Executive Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e7fcae2bf9240fd96295037bea49f7f-executive-administrative-assistant-reproductive-freedom-for-all-washington</t>
+  </si>
+  <si>
+    <t>Executive Assistant &amp; Board Liaison</t>
+  </si>
+  <si>
+    <t>The 5th Avenue Theatre</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61a15ba22209429480c99e110cf4d959-executive-assistant-board-liaison-the-5th-avenue-theatre-seattle</t>
+  </si>
+  <si>
+    <t>Executive Assistant &amp; Office Manager</t>
+  </si>
+  <si>
+    <t>FRESHFARM of Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 59000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f3c0f905307430882333c7a8891e3f2-executive-assistant-office-manager-freshfarm-of-washington-dc-washington</t>
+  </si>
+  <si>
+    <t>Colorado Education Association</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d161a9766be43c5a6254ea32ec1f58d-executive-director-colorado-education-association-denver</t>
+  </si>
+  <si>
+    <t>Arizona Education Association</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0604a2d8fc04b27abd47da43e8db7ee-executive-director-arizona-education-association-phoenix</t>
+  </si>
+  <si>
+    <t>RIVERE Ecological Center</t>
+  </si>
+  <si>
+    <t>Fredericksburg, Virginia</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c84865987224c85ae3705e28cad966a-executive-director-rivere-ecological-center-fredericksburg</t>
+  </si>
+  <si>
+    <t>Executive Director at Cambridge Neighbors</t>
+  </si>
+  <si>
+    <t>Cambridge Neighbors</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/790f2c5ec4c343ca8e25ec6dde4f3039-executive-director-at-cambridge-neighbors-cambridge-neighbors-cambridge</t>
+  </si>
+  <si>
+    <t>Executive Director, Community Partners for Affordable Housing</t>
+  </si>
+  <si>
+    <t>Kathy Kniep Consulting</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 167000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/defc8b3603e749b8818e7bbdc40d0448-executive-director-community-partners-for-affordable-housing-kathy-kniep-consulting-portland</t>
+  </si>
+  <si>
     <t>Freelancer season Fundraiser</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 50.00 - 100.00/month</t>
   </si>
   <si>
@@ -715,36 +1330,138 @@
     <t>PICO CALIFORNIA</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 160000.00 - 190000.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/948c3693472b47fa949eeee7252a59e8-general-counsel-pico-california-los-angeles</t>
   </si>
   <si>
+    <t>Gerente de Asuntos Institucionales, México</t>
+  </si>
+  <si>
+    <t>Mercy for Animals Latinoamérica</t>
+  </si>
+  <si>
+    <t>Remote (Ciudad de México, Ciudad de México, MX)</t>
+  </si>
+  <si>
+    <t>MXN 40000.00 - 45000.00/month</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfd544eb6c744291a3fdcadd7ea8ce62-gerente-de-asuntos-institucionales-mexico-mercy-for-animals-latinoamerica-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of Puget Sound</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 64500.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3ab36fd490845bbbdf58e2cf873c475-grants-manager-big-brothers-big-sisters-of-puget-sound-bellevue</t>
+  </si>
+  <si>
     <t>Immigration Attorney</t>
   </si>
   <si>
     <t>Asiyah Women's Center</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Community Development, Housing Homelessness</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bc6c3c0839174b4bb1f7f1c901fb5b03-immigration-attorney-asiyah-womens-center-kings-county</t>
   </si>
   <si>
+    <t>Immigration Pro Bono Coordinating Attorney</t>
+  </si>
+  <si>
+    <t>Legal Services NYC</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 103330.00 - 169852.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3b3b6ac9d0e4e0e8f10318c1c9b97d3-immigration-pro-bono-coordinating-attorney-legal-services-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Individual and Planned Giving Officer</t>
+  </si>
+  <si>
+    <t>Broadway Cares/Equity Fights AIDS</t>
+  </si>
+  <si>
+    <t>Arts Music, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c72ed68efb14ed7b663532cd426217a-individual-and-planned-giving-officer-broadway-caresequity-fights-aids-new-york</t>
+  </si>
+  <si>
+    <t>Infant &amp; Toddler Lead Teachers</t>
+  </si>
+  <si>
+    <t>Hope For New Haven</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/460fd8ab58fc442c8fd0b9a8492b31fb-infant-toddler-lead-teachers-hope-for-new-haven-new-haven</t>
+  </si>
+  <si>
+    <t>International Programs Administrator</t>
+  </si>
+  <si>
+    <t>Somatic Experiencing International</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40a58ec9880244fe826e170bfc3d77ed-international-programs-administrator-somatic-experiencing-international-boulder</t>
+  </si>
+  <si>
+    <t>Legal Education Manager</t>
+  </si>
+  <si>
+    <t>NJ LEEP (Law and Education Empowerment Project)</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8487ebacbf6c49588bb44f272882e621-legal-education-manager-nj-leep-law-and-education-empowerment-project-newark</t>
+  </si>
+  <si>
     <t>Managing Director for the US-China Music Institute</t>
   </si>
   <si>
@@ -757,33 +1474,162 @@
     <t>USD 70000.00 - 70000.00/year</t>
   </si>
   <si>
-    <t>Education, Arts Music</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/14fa5a26182941b6b90b4c65c4ba55bc-managing-director-for-the-us-china-music-institute-bard-college-red-hook</t>
   </si>
   <si>
+    <t>Membership Coordinator</t>
+  </si>
+  <si>
+    <t>First Church in Boston</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/803bf5a8f7914fb4a804d4112b2b3169-membership-coordinator-first-church-in-boston-boston</t>
+  </si>
+  <si>
+    <t>Northern California Organizer</t>
+  </si>
+  <si>
+    <t>USD 68640.00 - 68640.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a6d56791d2d47409bb5ef6721743887-northern-california-organizer-reproductive-freedom-for-all-san-francisco</t>
+  </si>
+  <si>
     <t>NYC Program Facilitator (Spanish Fluency Required)</t>
   </si>
   <si>
     <t>Pajama Program</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 30.00 - 35.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3e7d02f41bb24151aabbcae0509e057d-nyc-program-facilitator-spanish-fluency-required-pajama-program-new-york</t>
   </si>
   <si>
+    <t>Beyond Bedtime (formerly Pajama Program)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e7d02f41bb24151aabbcae0509e057d-nyc-program-facilitator-spanish-fluency-required-beyond-bedtime-formerly-pajama-program-new-york</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>Point Blue Conservation Science</t>
+  </si>
+  <si>
+    <t>Petaluma, California</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c218247f51c48289b07f54b7ed4b333-philanthropy-officer-point-blue-conservation-science-petaluma</t>
+  </si>
+  <si>
+    <t>Preschool Lead Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f592cb2cfd6146bba87d8aa5230eb80c-preschool-lead-teacher-hope-for-new-haven-new-haven</t>
+  </si>
+  <si>
+    <t>Procurement Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39218c05417144549b049a5a295a8eea-procurement-manager-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Program and Policy Manager (Full-time Remote)</t>
+  </si>
+  <si>
+    <t>Safe Routes Partnership</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/561e0cac5c3e454ebe34ede86449351e-program-and-policy-manager-full-time-remote-safe-routes-partnership-fairfax</t>
+  </si>
+  <si>
+    <t>Program Associate, Governors Safeguarding Democracy</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance</t>
+  </si>
+  <si>
+    <t>Policy, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc030169c4bc49a8855eb5e2c0198153-program-associate-governors-safeguarding-democracy-governors-action-alliance-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/440e979164ca487682a6e810a642878e-program-coordinator-nj-leep-law-and-education-empowerment-project-newark</t>
+  </si>
+  <si>
+    <t>RADCo Intake Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25d892af4eae4ebe857f7f63151b5dee-radco-intake-specialist-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>Regional Operations Associate (ROA)</t>
+  </si>
+  <si>
+    <t>Share My Meals</t>
+  </si>
+  <si>
+    <t>Princeton, New Jersey</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/086a314014514a4e9e36edf4a0119f9a-regional-operations-associate-roa-share-my-meals-princeton</t>
+  </si>
+  <si>
+    <t>Residential Program Director</t>
+  </si>
+  <si>
+    <t>Seneca Family of Agencies</t>
+  </si>
+  <si>
+    <t>Salinas, CA</t>
+  </si>
+  <si>
+    <t>USD 120707.00 - 134707.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69748a80456a4dccbe911554b8c9f3d2-residential-program-director-seneca-family-of-agencies-salinas</t>
+  </si>
+  <si>
+    <t>Right To Counsel Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0386eca30ed54bdfb243b73c63f9b675-right-to-counsel-coordinator-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
     <t>SAWSO 50th Anniversary Planning Coordinator</t>
   </si>
   <si>
@@ -808,12 +1654,123 @@
     <t>Centereach, New York</t>
   </si>
   <si>
-    <t>USD 65000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/f7955bb9612549cbba15ded533143879-senior-organizer-suffolk-county-regional-office-new-york-civil-liberties-union-foundation-centereach</t>
   </si>
   <si>
+    <t>Senior Program Associate</t>
+  </si>
+  <si>
+    <t>PureLegacee</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42e1cb8393ab4a888c8e3290b8100d80-senior-program-associate-purelegacee-brooklyn</t>
+  </si>
+  <si>
+    <t>Senior SNAP Policy Analyst</t>
+  </si>
+  <si>
+    <t>Food Research &amp; Action Center (FRAC)</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9902a2e67da4486e863ac20d2e8a2a1e-senior-snap-policy-analyst-food-research-action-center-frac-washington</t>
+  </si>
+  <si>
+    <t>Shelter Client Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18c48070f26e4ff99c13127eacc93cb4-shelter-client-advocate-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>Social Practitioner - Bilingual (Mandarin/Cantonese)</t>
+  </si>
+  <si>
+    <t>New York Disaster Interfaith Services (NYDIS)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Religion Spirituality, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c694587921e44369d00655386b03371-social-practitioner-bilingual-mandarincantonese-new-york-disaster-interfaith-services-nydis-new-york</t>
+  </si>
+  <si>
+    <t>Sourcing Lead, Supply Chain &amp; Compliance</t>
+  </si>
+  <si>
+    <t>GrowNYC</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/905a685d57d341dd8fd54e3ae18f1c67-sourcing-lead-supply-chain-compliance-grownyc-bronx-county</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>San Francisco Zoo &amp; Gardens</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/305bed46255e4db1b9b5411b23719cbe-staff-accountant-san-francisco-zoo-gardens-san-francisco</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c065dd8300b4609b3d337e33024daf3-staff-attorney-immigration-center-for-women-and-children-los-angeles</t>
+  </si>
+  <si>
+    <t>SeniorLAW Center</t>
+  </si>
+  <si>
+    <t>USD 66000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0dd6a2a72cf42bca1773f82b5fa4aff-staff-attorney-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
     <t>Staff Attorney, Public Benefits Law Unit</t>
   </si>
   <si>
@@ -821,6 +1778,93 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/f7bed75afb314e42bc2b2c8e04469574-staff-attorney-public-benefits-law-unit-legal-aid-dc-washington</t>
+  </si>
+  <si>
+    <t>Stop Data Centers Canvass Director</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Remote (Allentown, Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 54200.00 - 71800.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3245e42f92448ee95275ab02c1089aa-stop-data-centers-canvass-director-food-water-watch-allentown</t>
+  </si>
+  <si>
+    <t>Systems Administrator</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 96213.00 - 106903.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a9a089340d948bb9261254276c03641-systems-administrator-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Tenant Services Coordinator, Master Lease Program - 315 W 94th</t>
+  </si>
+  <si>
+    <t>USD 29.67 - 32.97/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Substance Abuse Addiction, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e35a96d804354d79ac0dbb99571a37f4-tenant-services-coordinator-master-lease-program-315-w-94th-riseboro-community-partnership-new-york</t>
+  </si>
+  <si>
+    <t>Thriving Communities Project Coordinator</t>
+  </si>
+  <si>
+    <t>Beyond Toxics</t>
+  </si>
+  <si>
+    <t>USD 5007.58 - 6009.10/month</t>
+  </si>
+  <si>
+    <t>Environment, Energy, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f174ca930c2c4d1992cfe4db8dd2789b-thriving-communities-project-coordinator-beyond-toxics-eugene</t>
+  </si>
+  <si>
+    <t>Ticketing &amp; Auction Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec907f59da3e4ee0887d6b971deeba68-ticketing-auction-coordinator-broadway-caresequity-fights-aids-new-york</t>
+  </si>
+  <si>
+    <t>Way Finders - Legal Assistant</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 25.50 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/799dc504f4b14d06a3a1f29b15330fb7-way-finders-legal-assistant-neighborworks-affiliates-springfield</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1296,666 +2340,689 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
+      <c r="H10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
+      <c r="H11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
+      <c r="H16" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
         <v>132</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" t="s">
-        <v>137</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
         <v>139</v>
       </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="H25" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" t="s">
-        <v>142</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
         <v>153</v>
       </c>
-      <c r="B28" t="s">
-        <v>154</v>
-      </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="F29" t="s">
-        <v>148</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="F31" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
         <v>171</v>
       </c>
-      <c r="F32" t="s">
+      <c r="C33" t="s">
         <v>172</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
         <v>173</v>
+      </c>
+      <c r="F33" t="s">
+        <v>174</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1992,6 +3059,7 @@
     <hyperlink ref="H30" r:id="rId29"/>
     <hyperlink ref="H31" r:id="rId30"/>
     <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2048,7 +3116,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2089,393 +3157,2072 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="E11" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B13" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F13" t="s">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F14" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="E15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B17" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F17" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E18" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F18" t="s">
+        <v>273</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" t="s">
         <v>197</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="D20" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" t="s">
+        <v>283</v>
+      </c>
+      <c r="F20" t="s">
+        <v>284</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D21" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" t="s">
+        <v>289</v>
+      </c>
+      <c r="F21" t="s">
+        <v>181</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>291</v>
+      </c>
+      <c r="B22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D22" t="s">
+        <v>179</v>
+      </c>
+      <c r="E22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F22" t="s">
+        <v>295</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" t="s">
+        <v>299</v>
+      </c>
+      <c r="F23" t="s">
+        <v>181</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F24" t="s">
+        <v>305</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B25" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" t="s">
+        <v>308</v>
+      </c>
+      <c r="F25" t="s">
+        <v>309</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26" t="s">
+        <v>314</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" t="s">
+        <v>318</v>
+      </c>
+      <c r="F27" t="s">
+        <v>319</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" t="s">
+        <v>323</v>
+      </c>
+      <c r="D28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" t="s">
+        <v>324</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" t="s">
+        <v>327</v>
+      </c>
+      <c r="C29" t="s">
+        <v>328</v>
+      </c>
+      <c r="D29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29" t="s">
+        <v>329</v>
+      </c>
+      <c r="F29" t="s">
+        <v>330</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" t="s">
+        <v>334</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>336</v>
+      </c>
+      <c r="B31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C31" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E31" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" t="s">
+        <v>338</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" t="s">
+        <v>342</v>
+      </c>
+      <c r="D32" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" t="s">
+        <v>344</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>346</v>
+      </c>
+      <c r="B33" t="s">
+        <v>347</v>
+      </c>
+      <c r="C33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" t="s">
+        <v>350</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>352</v>
+      </c>
+      <c r="B34" t="s">
+        <v>353</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" t="s">
+        <v>354</v>
+      </c>
+      <c r="F34" t="s">
+        <v>355</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" t="s">
+        <v>358</v>
+      </c>
+      <c r="C35" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" t="s">
+        <v>359</v>
+      </c>
+      <c r="F35" t="s">
+        <v>360</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>362</v>
+      </c>
+      <c r="B36" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" t="s">
+        <v>364</v>
+      </c>
+      <c r="D36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" t="s">
+        <v>365</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>367</v>
+      </c>
+      <c r="B37" t="s">
+        <v>368</v>
+      </c>
+      <c r="C37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" t="s">
+        <v>369</v>
+      </c>
+      <c r="F37" t="s">
+        <v>370</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>372</v>
+      </c>
+      <c r="B38" t="s">
+        <v>373</v>
+      </c>
+      <c r="C38" t="s">
+        <v>374</v>
+      </c>
+      <c r="D38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" t="s">
+        <v>375</v>
+      </c>
+      <c r="F38" t="s">
+        <v>376</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>378</v>
+      </c>
+      <c r="B39" t="s">
+        <v>379</v>
+      </c>
+      <c r="C39" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
+      </c>
+      <c r="E39" t="s">
+        <v>380</v>
+      </c>
+      <c r="F39" t="s">
+        <v>381</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>383</v>
+      </c>
+      <c r="B40" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" t="s">
+        <v>222</v>
+      </c>
+      <c r="E40" t="s">
+        <v>385</v>
+      </c>
+      <c r="F40" t="s">
+        <v>257</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" t="s">
         <v>268</v>
+      </c>
+      <c r="F41" t="s">
+        <v>389</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>391</v>
+      </c>
+      <c r="B42" t="s">
+        <v>392</v>
+      </c>
+      <c r="C42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" t="s">
+        <v>393</v>
+      </c>
+      <c r="F42" t="s">
+        <v>394</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>396</v>
+      </c>
+      <c r="B43" t="s">
+        <v>397</v>
+      </c>
+      <c r="C43" t="s">
+        <v>398</v>
+      </c>
+      <c r="D43" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" t="s">
+        <v>399</v>
+      </c>
+      <c r="F43" t="s">
+        <v>187</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>401</v>
+      </c>
+      <c r="B44" t="s">
+        <v>402</v>
+      </c>
+      <c r="C44" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E44" t="s">
+        <v>403</v>
+      </c>
+      <c r="F44" t="s">
+        <v>404</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>406</v>
+      </c>
+      <c r="C45" t="s">
+        <v>407</v>
+      </c>
+      <c r="D45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E45" t="s">
+        <v>408</v>
+      </c>
+      <c r="F45" t="s">
+        <v>409</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46" t="s">
+        <v>412</v>
+      </c>
+      <c r="D46" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" t="s">
+        <v>413</v>
+      </c>
+      <c r="F46" t="s">
+        <v>414</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" t="s">
+        <v>417</v>
+      </c>
+      <c r="D47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" t="s">
+        <v>375</v>
+      </c>
+      <c r="F47" t="s">
+        <v>418</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>420</v>
+      </c>
+      <c r="B48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C48" t="s">
+        <v>422</v>
+      </c>
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" t="s">
+        <v>250</v>
+      </c>
+      <c r="F48" t="s">
+        <v>423</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>425</v>
+      </c>
+      <c r="B49" t="s">
+        <v>426</v>
+      </c>
+      <c r="C49" t="s">
+        <v>427</v>
+      </c>
+      <c r="D49" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" t="s">
+        <v>428</v>
+      </c>
+      <c r="F49" t="s">
+        <v>429</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>431</v>
+      </c>
+      <c r="B50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" t="s">
+        <v>433</v>
+      </c>
+      <c r="F50" t="s">
+        <v>434</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>436</v>
+      </c>
+      <c r="B51" t="s">
+        <v>437</v>
+      </c>
+      <c r="C51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" t="s">
+        <v>179</v>
+      </c>
+      <c r="E51" t="s">
+        <v>438</v>
+      </c>
+      <c r="F51" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" t="s">
+        <v>441</v>
+      </c>
+      <c r="C52" t="s">
+        <v>442</v>
+      </c>
+      <c r="D52" t="s">
+        <v>179</v>
+      </c>
+      <c r="E52" t="s">
+        <v>443</v>
+      </c>
+      <c r="F52" t="s">
+        <v>444</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>446</v>
+      </c>
+      <c r="B53" t="s">
+        <v>447</v>
+      </c>
+      <c r="C53" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" t="s">
+        <v>179</v>
+      </c>
+      <c r="E53" t="s">
+        <v>449</v>
+      </c>
+      <c r="F53" t="s">
+        <v>450</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>452</v>
+      </c>
+      <c r="B54" t="s">
+        <v>453</v>
+      </c>
+      <c r="C54" t="s">
+        <v>261</v>
+      </c>
+      <c r="D54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" t="s">
+        <v>268</v>
+      </c>
+      <c r="F54" t="s">
+        <v>454</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>456</v>
+      </c>
+      <c r="B55" t="s">
+        <v>457</v>
+      </c>
+      <c r="C55" t="s">
+        <v>458</v>
+      </c>
+      <c r="D55" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" t="s">
+        <v>459</v>
+      </c>
+      <c r="F55" t="s">
+        <v>460</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>462</v>
+      </c>
+      <c r="B56" t="s">
+        <v>463</v>
+      </c>
+      <c r="C56" t="s">
+        <v>244</v>
+      </c>
+      <c r="D56" t="s">
+        <v>179</v>
+      </c>
+      <c r="E56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F56" t="s">
+        <v>464</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>466</v>
+      </c>
+      <c r="B57" t="s">
+        <v>467</v>
+      </c>
+      <c r="C57" t="s">
+        <v>468</v>
+      </c>
+      <c r="D57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57" t="s">
+        <v>469</v>
+      </c>
+      <c r="F57" t="s">
+        <v>470</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>472</v>
+      </c>
+      <c r="B58" t="s">
+        <v>473</v>
+      </c>
+      <c r="C58" t="s">
+        <v>197</v>
+      </c>
+      <c r="D58" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" t="s">
+        <v>474</v>
+      </c>
+      <c r="F58" t="s">
+        <v>475</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>477</v>
+      </c>
+      <c r="B59" t="s">
+        <v>478</v>
+      </c>
+      <c r="C59" t="s">
+        <v>303</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" t="s">
+        <v>479</v>
+      </c>
+      <c r="F59" t="s">
+        <v>480</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>482</v>
+      </c>
+      <c r="B60" t="s">
+        <v>483</v>
+      </c>
+      <c r="C60" t="s">
+        <v>484</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>485</v>
+      </c>
+      <c r="F60" t="s">
+        <v>365</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>487</v>
+      </c>
+      <c r="B61" t="s">
+        <v>488</v>
+      </c>
+      <c r="C61" t="s">
+        <v>489</v>
+      </c>
+      <c r="D61" t="s">
+        <v>222</v>
+      </c>
+      <c r="E61" t="s">
+        <v>490</v>
+      </c>
+      <c r="F61" t="s">
+        <v>491</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>493</v>
+      </c>
+      <c r="B62" t="s">
+        <v>392</v>
+      </c>
+      <c r="C62" t="s">
+        <v>328</v>
+      </c>
+      <c r="D62" t="s">
+        <v>179</v>
+      </c>
+      <c r="E62" t="s">
+        <v>494</v>
+      </c>
+      <c r="F62" t="s">
+        <v>394</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>496</v>
+      </c>
+      <c r="B63" t="s">
+        <v>497</v>
+      </c>
+      <c r="C63" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" t="s">
+        <v>222</v>
+      </c>
+      <c r="E63" t="s">
+        <v>498</v>
+      </c>
+      <c r="F63" t="s">
+        <v>295</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>496</v>
+      </c>
+      <c r="B64" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" t="s">
+        <v>222</v>
+      </c>
+      <c r="E64" t="s">
+        <v>498</v>
+      </c>
+      <c r="F64" t="s">
+        <v>295</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>502</v>
+      </c>
+      <c r="B65" t="s">
+        <v>503</v>
+      </c>
+      <c r="C65" t="s">
+        <v>504</v>
+      </c>
+      <c r="D65" t="s">
+        <v>179</v>
+      </c>
+      <c r="E65" t="s">
+        <v>272</v>
+      </c>
+      <c r="F65" t="s">
+        <v>505</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>507</v>
+      </c>
+      <c r="B66" t="s">
+        <v>467</v>
+      </c>
+      <c r="C66" t="s">
+        <v>468</v>
+      </c>
+      <c r="D66" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" t="s">
+        <v>469</v>
+      </c>
+      <c r="F66" t="s">
+        <v>470</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s">
+        <v>312</v>
+      </c>
+      <c r="C67" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" t="s">
+        <v>313</v>
+      </c>
+      <c r="F67" t="s">
+        <v>314</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>511</v>
+      </c>
+      <c r="B68" t="s">
+        <v>512</v>
+      </c>
+      <c r="C68" t="s">
+        <v>197</v>
+      </c>
+      <c r="D68" t="s">
+        <v>179</v>
+      </c>
+      <c r="E68" t="s">
+        <v>513</v>
+      </c>
+      <c r="F68" t="s">
+        <v>514</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>516</v>
+      </c>
+      <c r="B69" t="s">
+        <v>517</v>
+      </c>
+      <c r="C69" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" t="s">
+        <v>179</v>
+      </c>
+      <c r="E69" t="s">
+        <v>233</v>
+      </c>
+      <c r="F69" t="s">
+        <v>518</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>520</v>
+      </c>
+      <c r="B70" t="s">
+        <v>478</v>
+      </c>
+      <c r="C70" t="s">
+        <v>303</v>
+      </c>
+      <c r="D70" t="s">
+        <v>179</v>
+      </c>
+      <c r="E70" t="s">
+        <v>521</v>
+      </c>
+      <c r="F70" t="s">
+        <v>480</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>523</v>
+      </c>
+      <c r="B71" t="s">
+        <v>327</v>
+      </c>
+      <c r="C71" t="s">
+        <v>328</v>
+      </c>
+      <c r="D71" t="s">
+        <v>179</v>
+      </c>
+      <c r="E71" t="s">
+        <v>329</v>
+      </c>
+      <c r="F71" t="s">
+        <v>330</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>525</v>
+      </c>
+      <c r="B72" t="s">
+        <v>526</v>
+      </c>
+      <c r="C72" t="s">
+        <v>527</v>
+      </c>
+      <c r="D72" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" t="s">
+        <v>245</v>
+      </c>
+      <c r="F72" t="s">
+        <v>528</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>530</v>
+      </c>
+      <c r="B73" t="s">
+        <v>531</v>
+      </c>
+      <c r="C73" t="s">
+        <v>532</v>
+      </c>
+      <c r="D73" t="s">
+        <v>179</v>
+      </c>
+      <c r="E73" t="s">
+        <v>533</v>
+      </c>
+      <c r="F73" t="s">
+        <v>534</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>536</v>
+      </c>
+      <c r="B74" t="s">
+        <v>327</v>
+      </c>
+      <c r="C74" t="s">
+        <v>328</v>
+      </c>
+      <c r="D74" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" t="s">
+        <v>329</v>
+      </c>
+      <c r="F74" t="s">
+        <v>330</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>538</v>
+      </c>
+      <c r="B75" t="s">
+        <v>539</v>
+      </c>
+      <c r="C75" t="s">
+        <v>540</v>
+      </c>
+      <c r="D75" t="s">
+        <v>210</v>
+      </c>
+      <c r="E75" t="s">
+        <v>541</v>
+      </c>
+      <c r="F75" t="s">
+        <v>181</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>543</v>
+      </c>
+      <c r="B76" t="s">
+        <v>544</v>
+      </c>
+      <c r="C76" t="s">
+        <v>545</v>
+      </c>
+      <c r="D76" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76" t="s">
+        <v>399</v>
+      </c>
+      <c r="F76" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>547</v>
+      </c>
+      <c r="B77" t="s">
+        <v>548</v>
+      </c>
+      <c r="C77" t="s">
+        <v>549</v>
+      </c>
+      <c r="D77" t="s">
+        <v>222</v>
+      </c>
+      <c r="E77" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" t="s">
+        <v>550</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>552</v>
+      </c>
+      <c r="B78" t="s">
+        <v>553</v>
+      </c>
+      <c r="C78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D78" t="s">
+        <v>179</v>
+      </c>
+      <c r="E78" t="s">
+        <v>555</v>
+      </c>
+      <c r="F78" t="s">
+        <v>556</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>558</v>
+      </c>
+      <c r="B79" t="s">
+        <v>327</v>
+      </c>
+      <c r="C79" t="s">
+        <v>328</v>
+      </c>
+      <c r="D79" t="s">
+        <v>179</v>
+      </c>
+      <c r="E79" t="s">
+        <v>329</v>
+      </c>
+      <c r="F79" t="s">
+        <v>330</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>560</v>
+      </c>
+      <c r="B80" t="s">
+        <v>561</v>
+      </c>
+      <c r="C80" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" t="s">
+        <v>179</v>
+      </c>
+      <c r="E80" t="s">
+        <v>562</v>
+      </c>
+      <c r="F80" t="s">
+        <v>563</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>565</v>
+      </c>
+      <c r="B81" t="s">
+        <v>566</v>
+      </c>
+      <c r="C81" t="s">
+        <v>567</v>
+      </c>
+      <c r="D81" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" t="s">
+        <v>568</v>
+      </c>
+      <c r="F81" t="s">
+        <v>569</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>571</v>
+      </c>
+      <c r="B82" t="s">
+        <v>572</v>
+      </c>
+      <c r="C82" t="s">
+        <v>328</v>
+      </c>
+      <c r="D82" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" t="s">
+        <v>573</v>
+      </c>
+      <c r="F82" t="s">
+        <v>574</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>576</v>
+      </c>
+      <c r="B83" t="s">
+        <v>577</v>
+      </c>
+      <c r="C83" t="s">
+        <v>178</v>
+      </c>
+      <c r="D83" t="s">
+        <v>179</v>
+      </c>
+      <c r="E83" t="s">
+        <v>578</v>
+      </c>
+      <c r="F83" t="s">
+        <v>579</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>576</v>
+      </c>
+      <c r="B84" t="s">
+        <v>581</v>
+      </c>
+      <c r="C84" t="s">
+        <v>209</v>
+      </c>
+      <c r="D84" t="s">
+        <v>179</v>
+      </c>
+      <c r="E84" t="s">
+        <v>582</v>
+      </c>
+      <c r="F84" t="s">
+        <v>583</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>585</v>
+      </c>
+      <c r="B85" t="s">
+        <v>215</v>
+      </c>
+      <c r="C85" t="s">
+        <v>216</v>
+      </c>
+      <c r="D85" t="s">
+        <v>179</v>
+      </c>
+      <c r="E85" t="s">
+        <v>586</v>
+      </c>
+      <c r="F85" t="s">
+        <v>218</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>588</v>
+      </c>
+      <c r="B86" t="s">
+        <v>589</v>
+      </c>
+      <c r="C86" t="s">
+        <v>590</v>
+      </c>
+      <c r="D86" t="s">
+        <v>278</v>
+      </c>
+      <c r="E86" t="s">
+        <v>591</v>
+      </c>
+      <c r="F86" t="s">
+        <v>592</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>594</v>
+      </c>
+      <c r="B87" t="s">
+        <v>595</v>
+      </c>
+      <c r="C87" t="s">
+        <v>596</v>
+      </c>
+      <c r="D87" t="s">
+        <v>179</v>
+      </c>
+      <c r="E87" t="s">
+        <v>597</v>
+      </c>
+      <c r="F87" t="s">
+        <v>598</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>600</v>
+      </c>
+      <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>244</v>
+      </c>
+      <c r="D88" t="s">
+        <v>179</v>
+      </c>
+      <c r="E88" t="s">
+        <v>601</v>
+      </c>
+      <c r="F88" t="s">
+        <v>602</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>604</v>
+      </c>
+      <c r="B89" t="s">
+        <v>605</v>
+      </c>
+      <c r="C89" t="s">
+        <v>288</v>
+      </c>
+      <c r="D89" t="s">
+        <v>278</v>
+      </c>
+      <c r="E89" t="s">
+        <v>606</v>
+      </c>
+      <c r="F89" t="s">
+        <v>607</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>609</v>
+      </c>
+      <c r="B90" t="s">
+        <v>463</v>
+      </c>
+      <c r="C90" t="s">
+        <v>244</v>
+      </c>
+      <c r="D90" t="s">
+        <v>179</v>
+      </c>
+      <c r="E90" t="s">
+        <v>204</v>
+      </c>
+      <c r="F90" t="s">
+        <v>464</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>611</v>
+      </c>
+      <c r="B91" t="s">
+        <v>612</v>
+      </c>
+      <c r="C91" t="s">
+        <v>613</v>
+      </c>
+      <c r="D91" t="s">
+        <v>179</v>
+      </c>
+      <c r="E91" t="s">
+        <v>614</v>
+      </c>
+      <c r="F91" t="s">
+        <v>615</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -2498,6 +5245,79 @@
     <hyperlink ref="H16" r:id="rId15"/>
     <hyperlink ref="H17" r:id="rId16"/>
     <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-20.xlsx
+++ b/docs/xlsx/jobs-2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="622">
   <si>
     <t>Title</t>
   </si>
@@ -1520,6 +1520,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3e7d02f41bb24151aabbcae0509e057d-nyc-program-facilitator-spanish-fluency-required-beyond-bedtime-formerly-pajama-program-new-york</t>
+  </si>
+  <si>
+    <t>Operations &amp; Development Coordinator</t>
+  </si>
+  <si>
+    <t>Floodlight Inc</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f221371c65b2443f899ab67a8172cf3c-operations-development-coordinator-floodlight-inc-washington</t>
   </si>
   <si>
     <t>Philanthropy Officer</t>
@@ -3116,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4612,13 +4627,13 @@
         <v>503</v>
       </c>
       <c r="C65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" t="s">
+        <v>179</v>
+      </c>
+      <c r="E65" t="s">
         <v>504</v>
-      </c>
-      <c r="D65" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" t="s">
-        <v>272</v>
       </c>
       <c r="F65" t="s">
         <v>505</v>
@@ -4632,65 +4647,65 @@
         <v>507</v>
       </c>
       <c r="B66" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="C66" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="D66" t="s">
         <v>179</v>
       </c>
       <c r="E66" t="s">
-        <v>469</v>
+        <v>272</v>
       </c>
       <c r="F66" t="s">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s">
-        <v>312</v>
+        <v>467</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>468</v>
       </c>
       <c r="D67" t="s">
         <v>179</v>
       </c>
       <c r="E67" t="s">
-        <v>313</v>
+        <v>469</v>
       </c>
       <c r="F67" t="s">
-        <v>314</v>
+        <v>470</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s">
-        <v>512</v>
+        <v>312</v>
       </c>
       <c r="C68" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D68" t="s">
         <v>179</v>
       </c>
       <c r="E68" t="s">
-        <v>513</v>
+        <v>313</v>
       </c>
       <c r="F68" t="s">
-        <v>514</v>
+        <v>314</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>515</v>
@@ -4710,79 +4725,79 @@
         <v>179</v>
       </c>
       <c r="E69" t="s">
-        <v>233</v>
+        <v>518</v>
       </c>
       <c r="F69" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="C70" t="s">
-        <v>303</v>
+        <v>197</v>
       </c>
       <c r="D70" t="s">
         <v>179</v>
       </c>
       <c r="E70" t="s">
-        <v>521</v>
+        <v>233</v>
       </c>
       <c r="F70" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="C71" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
         <v>179</v>
       </c>
       <c r="E71" t="s">
-        <v>329</v>
+        <v>526</v>
       </c>
       <c r="F71" t="s">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B72" t="s">
-        <v>526</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s">
-        <v>527</v>
+        <v>328</v>
       </c>
       <c r="D72" t="s">
         <v>179</v>
       </c>
       <c r="E72" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="F72" t="s">
-        <v>528</v>
+        <v>330</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>529</v>
@@ -4802,56 +4817,56 @@
         <v>179</v>
       </c>
       <c r="E73" t="s">
+        <v>245</v>
+      </c>
+      <c r="F73" t="s">
         <v>533</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>535</v>
+      </c>
+      <c r="B74" t="s">
         <v>536</v>
       </c>
-      <c r="B74" t="s">
-        <v>327</v>
-      </c>
       <c r="C74" t="s">
-        <v>328</v>
+        <v>537</v>
       </c>
       <c r="D74" t="s">
         <v>179</v>
       </c>
       <c r="E74" t="s">
-        <v>329</v>
+        <v>538</v>
       </c>
       <c r="F74" t="s">
-        <v>330</v>
+        <v>539</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s">
-        <v>539</v>
+        <v>327</v>
       </c>
       <c r="C75" t="s">
-        <v>540</v>
+        <v>328</v>
       </c>
       <c r="D75" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
-        <v>541</v>
+        <v>329</v>
       </c>
       <c r="F75" t="s">
-        <v>181</v>
+        <v>330</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>542</v>
@@ -4868,36 +4883,36 @@
         <v>545</v>
       </c>
       <c r="D76" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>399</v>
+        <v>546</v>
       </c>
       <c r="F76" t="s">
         <v>181</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B77" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C77" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="E77" t="s">
+        <v>399</v>
+      </c>
+      <c r="F77" t="s">
         <v>181</v>
-      </c>
-      <c r="F77" t="s">
-        <v>550</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>551</v>
@@ -4914,59 +4929,59 @@
         <v>554</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="E78" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" t="s">
         <v>555</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>557</v>
+      </c>
+      <c r="B79" t="s">
         <v>558</v>
       </c>
-      <c r="B79" t="s">
-        <v>327</v>
-      </c>
       <c r="C79" t="s">
-        <v>328</v>
+        <v>559</v>
       </c>
       <c r="D79" t="s">
         <v>179</v>
       </c>
       <c r="E79" t="s">
-        <v>329</v>
+        <v>560</v>
       </c>
       <c r="F79" t="s">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s">
-        <v>561</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
-        <v>244</v>
+        <v>328</v>
       </c>
       <c r="D80" t="s">
         <v>179</v>
       </c>
       <c r="E80" t="s">
-        <v>562</v>
+        <v>329</v>
       </c>
       <c r="F80" t="s">
-        <v>563</v>
+        <v>330</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>564</v>
@@ -4980,30 +4995,30 @@
         <v>566</v>
       </c>
       <c r="C81" t="s">
+        <v>244</v>
+      </c>
+      <c r="D81" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" t="s">
         <v>567</v>
       </c>
-      <c r="D81" t="s">
-        <v>179</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>568</v>
       </c>
-      <c r="F81" t="s">
+      <c r="H81" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>570</v>
+      </c>
+      <c r="B82" t="s">
         <v>571</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>572</v>
-      </c>
-      <c r="C82" t="s">
-        <v>328</v>
       </c>
       <c r="D82" t="s">
         <v>179</v>
@@ -5026,7 +5041,7 @@
         <v>577</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>328</v>
       </c>
       <c r="D83" t="s">
         <v>179</v>
@@ -5043,131 +5058,131 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B84" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="D84" t="s">
         <v>179</v>
       </c>
       <c r="E84" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F84" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>586</v>
       </c>
       <c r="C85" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D85" t="s">
         <v>179</v>
       </c>
       <c r="E85" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F85" t="s">
-        <v>218</v>
+        <v>588</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B86" t="s">
-        <v>589</v>
+        <v>215</v>
       </c>
       <c r="C86" t="s">
-        <v>590</v>
+        <v>216</v>
       </c>
       <c r="D86" t="s">
-        <v>278</v>
+        <v>179</v>
       </c>
       <c r="E86" t="s">
         <v>591</v>
       </c>
       <c r="F86" t="s">
+        <v>218</v>
+      </c>
+      <c r="H86" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>593</v>
+      </c>
+      <c r="B87" t="s">
         <v>594</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>595</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87" t="s">
         <v>596</v>
       </c>
-      <c r="D87" t="s">
-        <v>179</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>597</v>
       </c>
-      <c r="F87" t="s">
+      <c r="H87" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>599</v>
+      </c>
+      <c r="B88" t="s">
         <v>600</v>
       </c>
-      <c r="B88" t="s">
-        <v>260</v>
-      </c>
       <c r="C88" t="s">
-        <v>244</v>
+        <v>601</v>
       </c>
       <c r="D88" t="s">
         <v>179</v>
       </c>
       <c r="E88" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F88" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B89" t="s">
-        <v>605</v>
+        <v>260</v>
       </c>
       <c r="C89" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="D89" t="s">
-        <v>278</v>
+        <v>179</v>
       </c>
       <c r="E89" t="s">
         <v>606</v>
@@ -5184,45 +5199,68 @@
         <v>609</v>
       </c>
       <c r="B90" t="s">
-        <v>463</v>
+        <v>610</v>
       </c>
       <c r="C90" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D90" t="s">
-        <v>179</v>
+        <v>278</v>
       </c>
       <c r="E90" t="s">
-        <v>204</v>
+        <v>611</v>
       </c>
       <c r="F90" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B91" t="s">
-        <v>612</v>
+        <v>463</v>
       </c>
       <c r="C91" t="s">
-        <v>613</v>
+        <v>244</v>
       </c>
       <c r="D91" t="s">
         <v>179</v>
       </c>
       <c r="E91" t="s">
-        <v>614</v>
+        <v>204</v>
       </c>
       <c r="F91" t="s">
+        <v>464</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="H91" s="2" t="s">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>616</v>
+      </c>
+      <c r="B92" t="s">
+        <v>617</v>
+      </c>
+      <c r="C92" t="s">
+        <v>618</v>
+      </c>
+      <c r="D92" t="s">
+        <v>179</v>
+      </c>
+      <c r="E92" t="s">
+        <v>619</v>
+      </c>
+      <c r="F92" t="s">
+        <v>620</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -5318,6 +5356,7 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-20.xlsx
+++ b/docs/xlsx/jobs-2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="623">
   <si>
     <t>Title</t>
   </si>
@@ -1130,6 +1130,9 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9c27161279ec494a959efd95a0a096ce-director-of-development-fort-greene-park-conservancy-kings-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c524f2ef0944482a89bc7ffddfe9877-director-of-development-policing-project-new-york</t>
   </si>
   <si>
     <t>Director of Editorial Events</t>
@@ -3131,7 +3134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4000,186 +4003,186 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>367</v>
+      </c>
+      <c r="B38" t="s">
+        <v>358</v>
+      </c>
+      <c r="C38" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" t="s">
+        <v>359</v>
+      </c>
+      <c r="F38" t="s">
+        <v>360</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="B38" t="s">
-        <v>373</v>
-      </c>
-      <c r="C38" t="s">
-        <v>374</v>
-      </c>
-      <c r="D38" t="s">
-        <v>179</v>
-      </c>
-      <c r="E38" t="s">
-        <v>375</v>
-      </c>
-      <c r="F38" t="s">
-        <v>376</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>373</v>
+      </c>
+      <c r="B39" t="s">
+        <v>374</v>
+      </c>
+      <c r="C39" t="s">
+        <v>375</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
+      </c>
+      <c r="E39" t="s">
+        <v>376</v>
+      </c>
+      <c r="F39" t="s">
+        <v>377</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="B39" t="s">
-        <v>379</v>
-      </c>
-      <c r="C39" t="s">
-        <v>244</v>
-      </c>
-      <c r="D39" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39" t="s">
-        <v>380</v>
-      </c>
-      <c r="F39" t="s">
-        <v>381</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C40" t="s">
         <v>244</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="E40" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F40" t="s">
-        <v>257</v>
+        <v>382</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C41" t="s">
         <v>244</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>268</v>
+        <v>386</v>
       </c>
       <c r="F41" t="s">
-        <v>389</v>
+        <v>257</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F42" t="s">
+        <v>390</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="B42" t="s">
-        <v>392</v>
-      </c>
-      <c r="C42" t="s">
-        <v>216</v>
-      </c>
-      <c r="D42" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" t="s">
-        <v>393</v>
-      </c>
-      <c r="F42" t="s">
-        <v>394</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>392</v>
+      </c>
+      <c r="B43" t="s">
+        <v>393</v>
+      </c>
+      <c r="C43" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" t="s">
+        <v>394</v>
+      </c>
+      <c r="F43" t="s">
+        <v>395</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="B43" t="s">
-        <v>397</v>
-      </c>
-      <c r="C43" t="s">
-        <v>398</v>
-      </c>
-      <c r="D43" t="s">
-        <v>179</v>
-      </c>
-      <c r="E43" t="s">
-        <v>399</v>
-      </c>
-      <c r="F43" t="s">
-        <v>187</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>397</v>
+      </c>
+      <c r="B44" t="s">
+        <v>398</v>
+      </c>
+      <c r="C44" t="s">
+        <v>399</v>
+      </c>
+      <c r="D44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E44" t="s">
+        <v>400</v>
+      </c>
+      <c r="F44" t="s">
+        <v>187</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="B44" t="s">
-        <v>402</v>
-      </c>
-      <c r="C44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D44" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" t="s">
-        <v>403</v>
-      </c>
-      <c r="F44" t="s">
-        <v>404</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>402</v>
       </c>
       <c r="B45" t="s">
+        <v>403</v>
+      </c>
+      <c r="C45" t="s">
+        <v>216</v>
+      </c>
+      <c r="D45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E45" t="s">
+        <v>404</v>
+      </c>
+      <c r="F45" t="s">
+        <v>405</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C45" t="s">
-        <v>407</v>
-      </c>
-      <c r="D45" t="s">
-        <v>179</v>
-      </c>
-      <c r="E45" t="s">
-        <v>408</v>
-      </c>
-      <c r="F45" t="s">
-        <v>409</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4187,22 +4190,22 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
+        <v>407</v>
+      </c>
+      <c r="C46" t="s">
+        <v>408</v>
+      </c>
+      <c r="D46" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" t="s">
+        <v>409</v>
+      </c>
+      <c r="F46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C46" t="s">
-        <v>412</v>
-      </c>
-      <c r="D46" t="s">
-        <v>179</v>
-      </c>
-      <c r="E46" t="s">
-        <v>413</v>
-      </c>
-      <c r="F46" t="s">
-        <v>414</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4210,398 +4213,398 @@
         <v>66</v>
       </c>
       <c r="B47" t="s">
+        <v>412</v>
+      </c>
+      <c r="C47" t="s">
+        <v>413</v>
+      </c>
+      <c r="D47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" t="s">
+        <v>414</v>
+      </c>
+      <c r="F47" t="s">
+        <v>415</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C47" t="s">
-        <v>417</v>
-      </c>
-      <c r="D47" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" t="s">
-        <v>375</v>
-      </c>
-      <c r="F47" t="s">
-        <v>418</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" t="s">
+        <v>376</v>
+      </c>
+      <c r="F48" t="s">
+        <v>419</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="B48" t="s">
-        <v>421</v>
-      </c>
-      <c r="C48" t="s">
-        <v>422</v>
-      </c>
-      <c r="D48" t="s">
-        <v>179</v>
-      </c>
-      <c r="E48" t="s">
-        <v>250</v>
-      </c>
-      <c r="F48" t="s">
-        <v>423</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>421</v>
+      </c>
+      <c r="B49" t="s">
+        <v>422</v>
+      </c>
+      <c r="C49" t="s">
+        <v>423</v>
+      </c>
+      <c r="D49" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" t="s">
+        <v>250</v>
+      </c>
+      <c r="F49" t="s">
+        <v>424</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B49" t="s">
-        <v>426</v>
-      </c>
-      <c r="C49" t="s">
-        <v>427</v>
-      </c>
-      <c r="D49" t="s">
-        <v>179</v>
-      </c>
-      <c r="E49" t="s">
-        <v>428</v>
-      </c>
-      <c r="F49" t="s">
-        <v>429</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>426</v>
+      </c>
+      <c r="B50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C50" t="s">
+        <v>428</v>
+      </c>
+      <c r="D50" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" t="s">
+        <v>429</v>
+      </c>
+      <c r="F50" t="s">
+        <v>430</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C50" t="s">
-        <v>197</v>
-      </c>
-      <c r="D50" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" t="s">
-        <v>433</v>
-      </c>
-      <c r="F50" t="s">
-        <v>434</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B51" t="s">
+        <v>433</v>
+      </c>
+      <c r="C51" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" t="s">
+        <v>434</v>
+      </c>
+      <c r="F51" t="s">
+        <v>435</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="B51" t="s">
-        <v>437</v>
-      </c>
-      <c r="C51" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" t="s">
-        <v>179</v>
-      </c>
-      <c r="E51" t="s">
-        <v>438</v>
-      </c>
-      <c r="F51" t="s">
-        <v>181</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>437</v>
+      </c>
+      <c r="B52" t="s">
+        <v>438</v>
+      </c>
+      <c r="C52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" t="s">
+        <v>179</v>
+      </c>
+      <c r="E52" t="s">
+        <v>439</v>
+      </c>
+      <c r="F52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B52" t="s">
-        <v>441</v>
-      </c>
-      <c r="C52" t="s">
-        <v>442</v>
-      </c>
-      <c r="D52" t="s">
-        <v>179</v>
-      </c>
-      <c r="E52" t="s">
-        <v>443</v>
-      </c>
-      <c r="F52" t="s">
-        <v>444</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>441</v>
+      </c>
+      <c r="B53" t="s">
+        <v>442</v>
+      </c>
+      <c r="C53" t="s">
+        <v>443</v>
+      </c>
+      <c r="D53" t="s">
+        <v>179</v>
+      </c>
+      <c r="E53" t="s">
+        <v>444</v>
+      </c>
+      <c r="F53" t="s">
+        <v>445</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B53" t="s">
-        <v>447</v>
-      </c>
-      <c r="C53" t="s">
-        <v>448</v>
-      </c>
-      <c r="D53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E53" t="s">
-        <v>449</v>
-      </c>
-      <c r="F53" t="s">
-        <v>450</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>447</v>
+      </c>
+      <c r="B54" t="s">
+        <v>448</v>
+      </c>
+      <c r="C54" t="s">
+        <v>449</v>
+      </c>
+      <c r="D54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" t="s">
+        <v>450</v>
+      </c>
+      <c r="F54" t="s">
+        <v>451</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B54" t="s">
-        <v>453</v>
-      </c>
-      <c r="C54" t="s">
-        <v>261</v>
-      </c>
-      <c r="D54" t="s">
-        <v>179</v>
-      </c>
-      <c r="E54" t="s">
-        <v>268</v>
-      </c>
-      <c r="F54" t="s">
-        <v>454</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>453</v>
+      </c>
+      <c r="B55" t="s">
+        <v>454</v>
+      </c>
+      <c r="C55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D55" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" t="s">
+        <v>268</v>
+      </c>
+      <c r="F55" t="s">
+        <v>455</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="B55" t="s">
-        <v>457</v>
-      </c>
-      <c r="C55" t="s">
-        <v>458</v>
-      </c>
-      <c r="D55" t="s">
-        <v>179</v>
-      </c>
-      <c r="E55" t="s">
-        <v>459</v>
-      </c>
-      <c r="F55" t="s">
-        <v>460</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>457</v>
+      </c>
+      <c r="B56" t="s">
+        <v>458</v>
+      </c>
+      <c r="C56" t="s">
+        <v>459</v>
+      </c>
+      <c r="D56" t="s">
+        <v>179</v>
+      </c>
+      <c r="E56" t="s">
+        <v>460</v>
+      </c>
+      <c r="F56" t="s">
+        <v>461</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="B56" t="s">
-        <v>463</v>
-      </c>
-      <c r="C56" t="s">
-        <v>244</v>
-      </c>
-      <c r="D56" t="s">
-        <v>179</v>
-      </c>
-      <c r="E56" t="s">
-        <v>204</v>
-      </c>
-      <c r="F56" t="s">
-        <v>464</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>463</v>
+      </c>
+      <c r="B57" t="s">
+        <v>464</v>
+      </c>
+      <c r="C57" t="s">
+        <v>244</v>
+      </c>
+      <c r="D57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57" t="s">
+        <v>204</v>
+      </c>
+      <c r="F57" t="s">
+        <v>465</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="B57" t="s">
-        <v>467</v>
-      </c>
-      <c r="C57" t="s">
-        <v>468</v>
-      </c>
-      <c r="D57" t="s">
-        <v>179</v>
-      </c>
-      <c r="E57" t="s">
-        <v>469</v>
-      </c>
-      <c r="F57" t="s">
-        <v>470</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>467</v>
+      </c>
+      <c r="B58" t="s">
+        <v>468</v>
+      </c>
+      <c r="C58" t="s">
+        <v>469</v>
+      </c>
+      <c r="D58" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" t="s">
+        <v>470</v>
+      </c>
+      <c r="F58" t="s">
+        <v>471</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="B58" t="s">
-        <v>473</v>
-      </c>
-      <c r="C58" t="s">
-        <v>197</v>
-      </c>
-      <c r="D58" t="s">
-        <v>179</v>
-      </c>
-      <c r="E58" t="s">
-        <v>474</v>
-      </c>
-      <c r="F58" t="s">
-        <v>475</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>473</v>
+      </c>
+      <c r="B59" t="s">
+        <v>474</v>
+      </c>
+      <c r="C59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" t="s">
+        <v>475</v>
+      </c>
+      <c r="F59" t="s">
+        <v>476</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B59" t="s">
-        <v>478</v>
-      </c>
-      <c r="C59" t="s">
-        <v>303</v>
-      </c>
-      <c r="D59" t="s">
-        <v>179</v>
-      </c>
-      <c r="E59" t="s">
-        <v>479</v>
-      </c>
-      <c r="F59" t="s">
-        <v>480</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>478</v>
+      </c>
+      <c r="B60" t="s">
+        <v>479</v>
+      </c>
+      <c r="C60" t="s">
+        <v>303</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>480</v>
+      </c>
+      <c r="F60" t="s">
+        <v>481</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="B60" t="s">
-        <v>483</v>
-      </c>
-      <c r="C60" t="s">
-        <v>484</v>
-      </c>
-      <c r="D60" t="s">
-        <v>179</v>
-      </c>
-      <c r="E60" t="s">
-        <v>485</v>
-      </c>
-      <c r="F60" t="s">
-        <v>365</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s">
+        <v>484</v>
+      </c>
+      <c r="C61" t="s">
+        <v>485</v>
+      </c>
+      <c r="D61" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" t="s">
+        <v>486</v>
+      </c>
+      <c r="F61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B61" t="s">
-        <v>488</v>
-      </c>
-      <c r="C61" t="s">
-        <v>489</v>
-      </c>
-      <c r="D61" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" t="s">
-        <v>490</v>
-      </c>
-      <c r="F61" t="s">
-        <v>491</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>489</v>
+      </c>
+      <c r="C62" t="s">
+        <v>490</v>
+      </c>
+      <c r="D62" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" t="s">
+        <v>491</v>
+      </c>
+      <c r="F62" t="s">
+        <v>492</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B62" t="s">
-        <v>392</v>
-      </c>
-      <c r="C62" t="s">
-        <v>328</v>
-      </c>
-      <c r="D62" t="s">
-        <v>179</v>
-      </c>
-      <c r="E62" t="s">
-        <v>494</v>
-      </c>
-      <c r="F62" t="s">
-        <v>394</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>494</v>
+      </c>
+      <c r="B63" t="s">
+        <v>393</v>
+      </c>
+      <c r="C63" t="s">
+        <v>328</v>
+      </c>
+      <c r="D63" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" t="s">
+        <v>495</v>
+      </c>
+      <c r="F63" t="s">
+        <v>395</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="B63" t="s">
-        <v>497</v>
-      </c>
-      <c r="C63" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" t="s">
-        <v>222</v>
-      </c>
-      <c r="E63" t="s">
-        <v>498</v>
-      </c>
-      <c r="F63" t="s">
-        <v>295</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C64" t="s">
         <v>244</v>
@@ -4610,136 +4613,136 @@
         <v>222</v>
       </c>
       <c r="E64" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F64" t="s">
         <v>295</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>497</v>
+      </c>
+      <c r="B65" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" t="s">
+        <v>222</v>
+      </c>
+      <c r="E65" t="s">
+        <v>499</v>
+      </c>
+      <c r="F65" t="s">
+        <v>295</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="B65" t="s">
-        <v>503</v>
-      </c>
-      <c r="C65" t="s">
-        <v>197</v>
-      </c>
-      <c r="D65" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" t="s">
-        <v>504</v>
-      </c>
-      <c r="F65" t="s">
-        <v>505</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>503</v>
+      </c>
+      <c r="B66" t="s">
+        <v>504</v>
+      </c>
+      <c r="C66" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" t="s">
+        <v>505</v>
+      </c>
+      <c r="F66" t="s">
+        <v>506</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="B66" t="s">
-        <v>508</v>
-      </c>
-      <c r="C66" t="s">
-        <v>509</v>
-      </c>
-      <c r="D66" t="s">
-        <v>179</v>
-      </c>
-      <c r="E66" t="s">
-        <v>272</v>
-      </c>
-      <c r="F66" t="s">
-        <v>510</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>508</v>
+      </c>
+      <c r="B67" t="s">
+        <v>509</v>
+      </c>
+      <c r="C67" t="s">
+        <v>510</v>
+      </c>
+      <c r="D67" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" t="s">
+        <v>272</v>
+      </c>
+      <c r="F67" t="s">
+        <v>511</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B67" t="s">
-        <v>467</v>
-      </c>
-      <c r="C67" t="s">
-        <v>468</v>
-      </c>
-      <c r="D67" t="s">
-        <v>179</v>
-      </c>
-      <c r="E67" t="s">
-        <v>469</v>
-      </c>
-      <c r="F67" t="s">
-        <v>470</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>513</v>
+      </c>
+      <c r="B68" t="s">
+        <v>468</v>
+      </c>
+      <c r="C68" t="s">
+        <v>469</v>
+      </c>
+      <c r="D68" t="s">
+        <v>179</v>
+      </c>
+      <c r="E68" t="s">
+        <v>470</v>
+      </c>
+      <c r="F68" t="s">
+        <v>471</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="B68" t="s">
-        <v>312</v>
-      </c>
-      <c r="C68" t="s">
-        <v>178</v>
-      </c>
-      <c r="D68" t="s">
-        <v>179</v>
-      </c>
-      <c r="E68" t="s">
-        <v>313</v>
-      </c>
-      <c r="F68" t="s">
-        <v>314</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>515</v>
+      </c>
+      <c r="B69" t="s">
+        <v>312</v>
+      </c>
+      <c r="C69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" t="s">
+        <v>179</v>
+      </c>
+      <c r="E69" t="s">
+        <v>313</v>
+      </c>
+      <c r="F69" t="s">
+        <v>314</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B69" t="s">
-        <v>517</v>
-      </c>
-      <c r="C69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" t="s">
-        <v>179</v>
-      </c>
-      <c r="E69" t="s">
-        <v>518</v>
-      </c>
-      <c r="F69" t="s">
-        <v>519</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C70" t="s">
         <v>197</v>
@@ -4748,519 +4751,542 @@
         <v>179</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>519</v>
       </c>
       <c r="F70" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>522</v>
+      </c>
+      <c r="B71" t="s">
+        <v>523</v>
+      </c>
+      <c r="C71" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" t="s">
+        <v>179</v>
+      </c>
+      <c r="E71" t="s">
+        <v>233</v>
+      </c>
+      <c r="F71" t="s">
+        <v>524</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B71" t="s">
-        <v>478</v>
-      </c>
-      <c r="C71" t="s">
-        <v>303</v>
-      </c>
-      <c r="D71" t="s">
-        <v>179</v>
-      </c>
-      <c r="E71" t="s">
-        <v>526</v>
-      </c>
-      <c r="F71" t="s">
-        <v>480</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>526</v>
+      </c>
+      <c r="B72" t="s">
+        <v>479</v>
+      </c>
+      <c r="C72" t="s">
+        <v>303</v>
+      </c>
+      <c r="D72" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" t="s">
+        <v>527</v>
+      </c>
+      <c r="F72" t="s">
+        <v>481</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="B72" t="s">
-        <v>327</v>
-      </c>
-      <c r="C72" t="s">
-        <v>328</v>
-      </c>
-      <c r="D72" t="s">
-        <v>179</v>
-      </c>
-      <c r="E72" t="s">
-        <v>329</v>
-      </c>
-      <c r="F72" t="s">
-        <v>330</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>529</v>
+      </c>
+      <c r="B73" t="s">
+        <v>327</v>
+      </c>
+      <c r="C73" t="s">
+        <v>328</v>
+      </c>
+      <c r="D73" t="s">
+        <v>179</v>
+      </c>
+      <c r="E73" t="s">
+        <v>329</v>
+      </c>
+      <c r="F73" t="s">
+        <v>330</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B73" t="s">
-        <v>531</v>
-      </c>
-      <c r="C73" t="s">
-        <v>532</v>
-      </c>
-      <c r="D73" t="s">
-        <v>179</v>
-      </c>
-      <c r="E73" t="s">
-        <v>245</v>
-      </c>
-      <c r="F73" t="s">
-        <v>533</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>531</v>
+      </c>
+      <c r="B74" t="s">
+        <v>532</v>
+      </c>
+      <c r="C74" t="s">
+        <v>533</v>
+      </c>
+      <c r="D74" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" t="s">
+        <v>245</v>
+      </c>
+      <c r="F74" t="s">
+        <v>534</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="B74" t="s">
-        <v>536</v>
-      </c>
-      <c r="C74" t="s">
-        <v>537</v>
-      </c>
-      <c r="D74" t="s">
-        <v>179</v>
-      </c>
-      <c r="E74" t="s">
-        <v>538</v>
-      </c>
-      <c r="F74" t="s">
-        <v>539</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>536</v>
+      </c>
+      <c r="B75" t="s">
+        <v>537</v>
+      </c>
+      <c r="C75" t="s">
+        <v>538</v>
+      </c>
+      <c r="D75" t="s">
+        <v>179</v>
+      </c>
+      <c r="E75" t="s">
+        <v>539</v>
+      </c>
+      <c r="F75" t="s">
+        <v>540</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="B75" t="s">
-        <v>327</v>
-      </c>
-      <c r="C75" t="s">
-        <v>328</v>
-      </c>
-      <c r="D75" t="s">
-        <v>179</v>
-      </c>
-      <c r="E75" t="s">
-        <v>329</v>
-      </c>
-      <c r="F75" t="s">
-        <v>330</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>542</v>
+      </c>
+      <c r="B76" t="s">
+        <v>327</v>
+      </c>
+      <c r="C76" t="s">
+        <v>328</v>
+      </c>
+      <c r="D76" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76" t="s">
+        <v>329</v>
+      </c>
+      <c r="F76" t="s">
+        <v>330</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="B76" t="s">
-        <v>544</v>
-      </c>
-      <c r="C76" t="s">
-        <v>545</v>
-      </c>
-      <c r="D76" t="s">
-        <v>210</v>
-      </c>
-      <c r="E76" t="s">
-        <v>546</v>
-      </c>
-      <c r="F76" t="s">
-        <v>181</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C77" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E77" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="F77" t="s">
         <v>181</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>549</v>
+      </c>
+      <c r="B78" t="s">
+        <v>550</v>
+      </c>
+      <c r="C78" t="s">
+        <v>551</v>
+      </c>
+      <c r="D78" t="s">
+        <v>179</v>
+      </c>
+      <c r="E78" t="s">
+        <v>400</v>
+      </c>
+      <c r="F78" t="s">
+        <v>181</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B78" t="s">
-        <v>553</v>
-      </c>
-      <c r="C78" t="s">
-        <v>554</v>
-      </c>
-      <c r="D78" t="s">
-        <v>222</v>
-      </c>
-      <c r="E78" t="s">
-        <v>181</v>
-      </c>
-      <c r="F78" t="s">
-        <v>555</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>553</v>
+      </c>
+      <c r="B79" t="s">
+        <v>554</v>
+      </c>
+      <c r="C79" t="s">
+        <v>555</v>
+      </c>
+      <c r="D79" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79" t="s">
+        <v>181</v>
+      </c>
+      <c r="F79" t="s">
+        <v>556</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="B79" t="s">
-        <v>558</v>
-      </c>
-      <c r="C79" t="s">
-        <v>559</v>
-      </c>
-      <c r="D79" t="s">
-        <v>179</v>
-      </c>
-      <c r="E79" t="s">
-        <v>560</v>
-      </c>
-      <c r="F79" t="s">
-        <v>561</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>558</v>
+      </c>
+      <c r="B80" t="s">
+        <v>559</v>
+      </c>
+      <c r="C80" t="s">
+        <v>560</v>
+      </c>
+      <c r="D80" t="s">
+        <v>179</v>
+      </c>
+      <c r="E80" t="s">
+        <v>561</v>
+      </c>
+      <c r="F80" t="s">
+        <v>562</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B80" t="s">
-        <v>327</v>
-      </c>
-      <c r="C80" t="s">
-        <v>328</v>
-      </c>
-      <c r="D80" t="s">
-        <v>179</v>
-      </c>
-      <c r="E80" t="s">
-        <v>329</v>
-      </c>
-      <c r="F80" t="s">
-        <v>330</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>564</v>
+      </c>
+      <c r="B81" t="s">
+        <v>327</v>
+      </c>
+      <c r="C81" t="s">
+        <v>328</v>
+      </c>
+      <c r="D81" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" t="s">
+        <v>329</v>
+      </c>
+      <c r="F81" t="s">
+        <v>330</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B81" t="s">
-        <v>566</v>
-      </c>
-      <c r="C81" t="s">
-        <v>244</v>
-      </c>
-      <c r="D81" t="s">
-        <v>179</v>
-      </c>
-      <c r="E81" t="s">
-        <v>567</v>
-      </c>
-      <c r="F81" t="s">
-        <v>568</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>566</v>
+      </c>
+      <c r="B82" t="s">
+        <v>567</v>
+      </c>
+      <c r="C82" t="s">
+        <v>244</v>
+      </c>
+      <c r="D82" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" t="s">
+        <v>568</v>
+      </c>
+      <c r="F82" t="s">
+        <v>569</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="B82" t="s">
-        <v>571</v>
-      </c>
-      <c r="C82" t="s">
-        <v>572</v>
-      </c>
-      <c r="D82" t="s">
-        <v>179</v>
-      </c>
-      <c r="E82" t="s">
-        <v>573</v>
-      </c>
-      <c r="F82" t="s">
-        <v>574</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>571</v>
+      </c>
+      <c r="B83" t="s">
+        <v>572</v>
+      </c>
+      <c r="C83" t="s">
+        <v>573</v>
+      </c>
+      <c r="D83" t="s">
+        <v>179</v>
+      </c>
+      <c r="E83" t="s">
+        <v>574</v>
+      </c>
+      <c r="F83" t="s">
+        <v>575</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="B83" t="s">
-        <v>577</v>
-      </c>
-      <c r="C83" t="s">
-        <v>328</v>
-      </c>
-      <c r="D83" t="s">
-        <v>179</v>
-      </c>
-      <c r="E83" t="s">
-        <v>578</v>
-      </c>
-      <c r="F83" t="s">
-        <v>579</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>577</v>
+      </c>
+      <c r="B84" t="s">
+        <v>578</v>
+      </c>
+      <c r="C84" t="s">
+        <v>328</v>
+      </c>
+      <c r="D84" t="s">
+        <v>179</v>
+      </c>
+      <c r="E84" t="s">
+        <v>579</v>
+      </c>
+      <c r="F84" t="s">
+        <v>580</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B84" t="s">
-        <v>582</v>
-      </c>
-      <c r="C84" t="s">
-        <v>178</v>
-      </c>
-      <c r="D84" t="s">
-        <v>179</v>
-      </c>
-      <c r="E84" t="s">
-        <v>583</v>
-      </c>
-      <c r="F84" t="s">
-        <v>584</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s">
+        <v>583</v>
+      </c>
+      <c r="C85" t="s">
+        <v>178</v>
+      </c>
+      <c r="D85" t="s">
+        <v>179</v>
+      </c>
+      <c r="E85" t="s">
+        <v>584</v>
+      </c>
+      <c r="F85" t="s">
+        <v>585</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="C85" t="s">
-        <v>209</v>
-      </c>
-      <c r="D85" t="s">
-        <v>179</v>
-      </c>
-      <c r="E85" t="s">
-        <v>587</v>
-      </c>
-      <c r="F85" t="s">
-        <v>588</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>582</v>
+      </c>
+      <c r="B86" t="s">
+        <v>587</v>
+      </c>
+      <c r="C86" t="s">
+        <v>209</v>
+      </c>
+      <c r="D86" t="s">
+        <v>179</v>
+      </c>
+      <c r="E86" t="s">
+        <v>588</v>
+      </c>
+      <c r="F86" t="s">
+        <v>589</v>
+      </c>
+      <c r="H86" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="B86" t="s">
-        <v>215</v>
-      </c>
-      <c r="C86" t="s">
-        <v>216</v>
-      </c>
-      <c r="D86" t="s">
-        <v>179</v>
-      </c>
-      <c r="E86" t="s">
-        <v>591</v>
-      </c>
-      <c r="F86" t="s">
-        <v>218</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>591</v>
+      </c>
+      <c r="B87" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" t="s">
+        <v>179</v>
+      </c>
+      <c r="E87" t="s">
+        <v>592</v>
+      </c>
+      <c r="F87" t="s">
+        <v>218</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="B87" t="s">
-        <v>594</v>
-      </c>
-      <c r="C87" t="s">
-        <v>595</v>
-      </c>
-      <c r="D87" t="s">
-        <v>278</v>
-      </c>
-      <c r="E87" t="s">
-        <v>596</v>
-      </c>
-      <c r="F87" t="s">
-        <v>597</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>594</v>
+      </c>
+      <c r="B88" t="s">
+        <v>595</v>
+      </c>
+      <c r="C88" t="s">
+        <v>596</v>
+      </c>
+      <c r="D88" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" t="s">
+        <v>597</v>
+      </c>
+      <c r="F88" t="s">
+        <v>598</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B88" t="s">
-        <v>600</v>
-      </c>
-      <c r="C88" t="s">
-        <v>601</v>
-      </c>
-      <c r="D88" t="s">
-        <v>179</v>
-      </c>
-      <c r="E88" t="s">
-        <v>602</v>
-      </c>
-      <c r="F88" t="s">
-        <v>603</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>600</v>
+      </c>
+      <c r="B89" t="s">
+        <v>601</v>
+      </c>
+      <c r="C89" t="s">
+        <v>602</v>
+      </c>
+      <c r="D89" t="s">
+        <v>179</v>
+      </c>
+      <c r="E89" t="s">
+        <v>603</v>
+      </c>
+      <c r="F89" t="s">
+        <v>604</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B89" t="s">
-        <v>260</v>
-      </c>
-      <c r="C89" t="s">
-        <v>244</v>
-      </c>
-      <c r="D89" t="s">
-        <v>179</v>
-      </c>
-      <c r="E89" t="s">
-        <v>606</v>
-      </c>
-      <c r="F89" t="s">
-        <v>607</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>606</v>
+      </c>
+      <c r="B90" t="s">
+        <v>260</v>
+      </c>
+      <c r="C90" t="s">
+        <v>244</v>
+      </c>
+      <c r="D90" t="s">
+        <v>179</v>
+      </c>
+      <c r="E90" t="s">
+        <v>607</v>
+      </c>
+      <c r="F90" t="s">
+        <v>608</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="B90" t="s">
-        <v>610</v>
-      </c>
-      <c r="C90" t="s">
-        <v>288</v>
-      </c>
-      <c r="D90" t="s">
-        <v>278</v>
-      </c>
-      <c r="E90" t="s">
-        <v>611</v>
-      </c>
-      <c r="F90" t="s">
-        <v>612</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>610</v>
+      </c>
+      <c r="B91" t="s">
+        <v>611</v>
+      </c>
+      <c r="C91" t="s">
+        <v>288</v>
+      </c>
+      <c r="D91" t="s">
+        <v>278</v>
+      </c>
+      <c r="E91" t="s">
+        <v>612</v>
+      </c>
+      <c r="F91" t="s">
+        <v>613</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="B91" t="s">
-        <v>463</v>
-      </c>
-      <c r="C91" t="s">
-        <v>244</v>
-      </c>
-      <c r="D91" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" t="s">
-        <v>204</v>
-      </c>
-      <c r="F91" t="s">
-        <v>464</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>615</v>
+      </c>
+      <c r="B92" t="s">
+        <v>464</v>
+      </c>
+      <c r="C92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D92" t="s">
+        <v>179</v>
+      </c>
+      <c r="E92" t="s">
+        <v>204</v>
+      </c>
+      <c r="F92" t="s">
+        <v>465</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B92" t="s">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>617</v>
       </c>
-      <c r="C92" t="s">
+      <c r="B93" t="s">
         <v>618</v>
       </c>
-      <c r="D92" t="s">
-        <v>179</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="C93" t="s">
         <v>619</v>
       </c>
-      <c r="F92" t="s">
+      <c r="D93" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" t="s">
         <v>620</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="F93" t="s">
         <v>621</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -5357,6 +5383,7 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
